--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>57827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R6" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B7" t="n">
-        <v>57827</v>
+        <v>91808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R7" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137894</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548514</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015402</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137733</v>
+        <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548570</v>
+        <v>548514</v>
       </c>
       <c r="R11" t="n">
-        <v>7015444</v>
+        <v>7015402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137867</v>
+        <v>129137799</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548533</v>
+        <v>548685</v>
       </c>
       <c r="R14" t="n">
-        <v>7015374</v>
+        <v>7015011</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
         <v>79034</v>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137867</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548533</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R27" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R28" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137784</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548583</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015438</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,10 +3548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3559,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137756</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548564</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015377</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
         <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>80167</v>
+        <v>91978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R40" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>91975</v>
+        <v>80167</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R41" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R42" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,11 +4701,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4732,32 +4727,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R43" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4803,6 +4798,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>91805</v>
+        <v>80140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R46" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>80176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137880</v>
+        <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>91811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548645</v>
+        <v>548447</v>
       </c>
       <c r="R5" t="n">
-        <v>7015108</v>
+        <v>7015454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137777</v>
+        <v>129137880</v>
       </c>
       <c r="B6" t="n">
-        <v>57827</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548714</v>
+        <v>548645</v>
       </c>
       <c r="R6" t="n">
-        <v>7015050</v>
+        <v>7015108</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B7" t="n">
-        <v>91808</v>
+        <v>57827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R7" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129137904</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129137879</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137799</v>
+        <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548685</v>
+        <v>548533</v>
       </c>
       <c r="R14" t="n">
-        <v>7015011</v>
+        <v>7015374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137867</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548533</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015374</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137765</v>
+        <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>97533</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548554</v>
+        <v>548676</v>
       </c>
       <c r="R17" t="n">
-        <v>7015316</v>
+        <v>7015168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137734</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>91523</v>
+        <v>97536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548676</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015168</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R20" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R21" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R27" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R28" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137861</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>80168</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548652</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015105</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137861</v>
       </c>
       <c r="B31" t="n">
-        <v>91808</v>
+        <v>80169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548652</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>97530</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97527</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>91811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
         <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137864</v>
+        <v>129137741</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548644</v>
+        <v>548694</v>
       </c>
       <c r="R45" t="n">
-        <v>7015111</v>
+        <v>7015327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,6 +4997,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5023,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R46" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5120,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137741</v>
+        <v>129137807</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5131,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548694</v>
+        <v>548713</v>
       </c>
       <c r="R47" t="n">
-        <v>7015327</v>
+        <v>7015358</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B48" t="n">
-        <v>96775</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R48" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5523,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548701</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,11 +5599,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B52" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R52" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B53" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R53" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5816,6 +5816,103 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129137839</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bäckedalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>548676</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7015162</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80176</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137733</v>
+        <v>129137894</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548570</v>
+        <v>548514</v>
       </c>
       <c r="R8" t="n">
-        <v>7015444</v>
+        <v>7015402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R9" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137894</v>
+        <v>129137881</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548514</v>
+        <v>548591</v>
       </c>
       <c r="R11" t="n">
-        <v>7015402</v>
+        <v>7015389</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R20" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R21" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>97530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>91811</v>
+        <v>80141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R44" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137741</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548694</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015327</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,11 +4997,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5028,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137864</v>
+        <v>129137741</v>
       </c>
       <c r="B46" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548644</v>
+        <v>548694</v>
       </c>
       <c r="R46" t="n">
-        <v>7015111</v>
+        <v>7015327</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5099,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R47" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B52" t="n">
         <v>91526</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R52" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B53" t="n">
         <v>91526</v>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R53" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>80176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R20" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R21" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,10 +3456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3467,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137861</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>80169</v>
+        <v>91811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548652</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015105</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137760</v>
+        <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548553</v>
+        <v>548565</v>
       </c>
       <c r="R4" t="n">
-        <v>7015318</v>
+        <v>7015377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B5" t="n">
-        <v>91811</v>
+        <v>57827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R5" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B7" t="n">
-        <v>57827</v>
+        <v>91811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R7" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137733</v>
+        <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548570</v>
+        <v>548591</v>
       </c>
       <c r="R9" t="n">
-        <v>7015444</v>
+        <v>7015389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R11" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R20" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R21" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R27" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R28" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3527,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97530</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B44" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R44" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>91811</v>
+        <v>80141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R47" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137856</v>
+        <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548522</v>
+        <v>548701</v>
       </c>
       <c r="R48" t="n">
-        <v>7015382</v>
+        <v>7015210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
         <v>57723</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B50" t="n">
         <v>57723</v>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5528,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
-        <v>96778</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80176</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137760</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548553</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015318</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R4" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137777</v>
+        <v>129137880</v>
       </c>
       <c r="B5" t="n">
-        <v>57827</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548714</v>
+        <v>548645</v>
       </c>
       <c r="R5" t="n">
-        <v>7015050</v>
+        <v>7015108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137880</v>
+        <v>129137777</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>57829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548645</v>
+        <v>548714</v>
       </c>
       <c r="R6" t="n">
-        <v>7015108</v>
+        <v>7015050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,7 +1168,7 @@
         <v>129137865</v>
       </c>
       <c r="B7" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137894</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548514</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015402</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1362,7 @@
         <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1459,7 @@
         <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137733</v>
+        <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548570</v>
+        <v>548514</v>
       </c>
       <c r="R11" t="n">
-        <v>7015444</v>
+        <v>7015402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>129137904</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129137879</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129137799</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R20" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R21" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R27" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R28" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,7 +3454,7 @@
         <v>129137784</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
         <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97530</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>97540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4046,7 +4046,7 @@
         <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B42" t="n">
-        <v>80176</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R42" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,6 +4701,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4727,32 +4732,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>80180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4762,10 +4767,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R43" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4798,11 +4803,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R44" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137755</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>91811</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548568</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015450</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137741</v>
+        <v>129137755</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548694</v>
+        <v>548568</v>
       </c>
       <c r="R46" t="n">
-        <v>7015327</v>
+        <v>7015450</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5094,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5120,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137864</v>
+        <v>129137741</v>
       </c>
       <c r="B47" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5131,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548644</v>
+        <v>548694</v>
       </c>
       <c r="R47" t="n">
-        <v>7015111</v>
+        <v>7015327</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B48" t="n">
-        <v>96778</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R48" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5319,32 +5324,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137823</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>96788</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5354,10 +5359,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548701</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5390,11 +5395,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5424,7 +5424,7 @@
         <v>129137743</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137867</v>
+        <v>129137799</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548533</v>
+        <v>548685</v>
       </c>
       <c r="R14" t="n">
-        <v>7015374</v>
+        <v>7015011</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137867</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>91818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548533</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>91818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137856</v>
+        <v>129137743</v>
       </c>
       <c r="B48" t="n">
         <v>57725</v>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548522</v>
+        <v>548589</v>
       </c>
       <c r="R48" t="n">
-        <v>7015382</v>
+        <v>7015420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,32 +5324,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137823</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
-        <v>96788</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548701</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015210</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,6 +5395,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5426,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B50" t="n">
         <v>57725</v>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R50" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5501,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137854</v>
+        <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>96788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548577</v>
+        <v>548701</v>
       </c>
       <c r="R51" t="n">
-        <v>7015456</v>
+        <v>7015210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,11 +5599,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>80180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B6" t="n">
-        <v>57829</v>
+        <v>91825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R6" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>57829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R7" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137733</v>
+        <v>129137808</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548570</v>
+        <v>548646</v>
       </c>
       <c r="R8" t="n">
-        <v>7015444</v>
+        <v>7015414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R9" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137808</v>
+        <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548646</v>
+        <v>548591</v>
       </c>
       <c r="R10" t="n">
-        <v>7015414</v>
+        <v>7015389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137799</v>
+        <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548685</v>
+        <v>548533</v>
       </c>
       <c r="R14" t="n">
-        <v>7015011</v>
+        <v>7015374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137867</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548533</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015374</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137734</v>
+        <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>97553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548676</v>
+        <v>548554</v>
       </c>
       <c r="R17" t="n">
-        <v>7015168</v>
+        <v>7015316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,32 +2354,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>97546</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548676</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R20" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R21" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>80173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R30" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3624,6 +3619,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137756</v>
       </c>
       <c r="B32" t="n">
-        <v>80173</v>
+        <v>91825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548564</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3860,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3920,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3949,7 +3949,7 @@
         <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>80180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R42" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,11 +4701,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4732,32 +4727,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>80180</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R43" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4803,6 +4798,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137864</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>80145</v>
+        <v>91825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548644</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015111</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,6 +4997,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5023,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137755</v>
+        <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548568</v>
+        <v>548713</v>
       </c>
       <c r="R46" t="n">
-        <v>7015450</v>
+        <v>7015358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5120,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5131,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R47" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137743</v>
+        <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>96795</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548589</v>
+        <v>548701</v>
       </c>
       <c r="R48" t="n">
-        <v>7015420</v>
+        <v>7015210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137856</v>
+        <v>129137743</v>
       </c>
       <c r="B50" t="n">
         <v>57725</v>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548522</v>
+        <v>548589</v>
       </c>
       <c r="R50" t="n">
-        <v>7015382</v>
+        <v>7015420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5528,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
-        <v>96788</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B52" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R52" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B53" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R53" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80180</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137880</v>
+        <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548645</v>
+        <v>548447</v>
       </c>
       <c r="R5" t="n">
-        <v>7015108</v>
+        <v>7015454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B6" t="n">
-        <v>91825</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R6" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137777</v>
+        <v>129137880</v>
       </c>
       <c r="B7" t="n">
-        <v>57829</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548714</v>
+        <v>548645</v>
       </c>
       <c r="R7" t="n">
-        <v>7015050</v>
+        <v>7015108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>129137808</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129137904</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129137879</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129137799</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>129137742</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137861</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>80173</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548652</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015105</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137784</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548583</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015438</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137756</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>91825</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548564</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015377</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3852,7 +3847,7 @@
         <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97547</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>91506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R38" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,32 +4334,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R39" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137741</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548694</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015327</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,11 +4997,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5028,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R46" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5099,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5128,7 +5128,7 @@
         <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>96795</v>
+        <v>96797</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,10 +5421,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5526,7 +5526,7 @@
         <v>129137856</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R52" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R53" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137865</v>
+        <v>129137880</v>
       </c>
       <c r="B5" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548447</v>
+        <v>548645</v>
       </c>
       <c r="R5" t="n">
-        <v>7015454</v>
+        <v>7015108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>91827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R6" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137880</v>
+        <v>129137777</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548645</v>
+        <v>548714</v>
       </c>
       <c r="R7" t="n">
-        <v>7015108</v>
+        <v>7015050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137808</v>
+        <v>129137894</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548646</v>
+        <v>548514</v>
       </c>
       <c r="R8" t="n">
-        <v>7015414</v>
+        <v>7015402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R10" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137894</v>
+        <v>129137881</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548514</v>
+        <v>548591</v>
       </c>
       <c r="R11" t="n">
-        <v>7015402</v>
+        <v>7015389</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137765</v>
+        <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>97555</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548554</v>
+        <v>548676</v>
       </c>
       <c r="R17" t="n">
-        <v>7015316</v>
+        <v>7015168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
         <v>97555</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137734</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>97555</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548676</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015168</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137841</v>
+        <v>129137742</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548505</v>
+        <v>548676</v>
       </c>
       <c r="R26" t="n">
-        <v>7015403</v>
+        <v>7015391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,6 +3124,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3150,10 +3155,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137742</v>
+        <v>129137841</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3166,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548676</v>
+        <v>548505</v>
       </c>
       <c r="R27" t="n">
-        <v>7015391</v>
+        <v>7015403</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,11 +3226,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137756</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548564</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137861</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548652</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015105</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,10 +3548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3559,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R44" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,6 +4997,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5023,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137741</v>
+        <v>129137755</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548694</v>
+        <v>548568</v>
       </c>
       <c r="R46" t="n">
-        <v>7015327</v>
+        <v>7015450</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5099,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B47" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R47" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>97549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548553</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137760</v>
+        <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548553</v>
+        <v>548565</v>
       </c>
       <c r="R4" t="n">
-        <v>7015318</v>
+        <v>7015377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3920,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B35" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137864</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548644</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015111</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137741</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548694</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015327</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,11 +4997,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5028,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B46" t="n">
-        <v>91827</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R46" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5125,10 +5120,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5131,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R47" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137760</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>97549</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548553</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015318</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>97575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R4" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137880</v>
+        <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548645</v>
+        <v>548447</v>
       </c>
       <c r="R5" t="n">
-        <v>7015108</v>
+        <v>7015454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137865</v>
+        <v>129137880</v>
       </c>
       <c r="B6" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548447</v>
+        <v>548645</v>
       </c>
       <c r="R6" t="n">
-        <v>7015454</v>
+        <v>7015108</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137894</v>
+        <v>129137881</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548514</v>
+        <v>548591</v>
       </c>
       <c r="R8" t="n">
-        <v>7015402</v>
+        <v>7015389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1362,7 @@
         <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137881</v>
+        <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548591</v>
+        <v>548514</v>
       </c>
       <c r="R11" t="n">
-        <v>7015389</v>
+        <v>7015402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137734</v>
+        <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>97581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548676</v>
+        <v>548554</v>
       </c>
       <c r="R17" t="n">
-        <v>7015168</v>
+        <v>7015316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,32 +2354,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>97555</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548676</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137742</v>
+        <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548676</v>
+        <v>548505</v>
       </c>
       <c r="R26" t="n">
-        <v>7015391</v>
+        <v>7015403</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,11 +3124,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3155,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137841</v>
+        <v>129137742</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3166,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3190,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548505</v>
+        <v>548676</v>
       </c>
       <c r="R27" t="n">
-        <v>7015403</v>
+        <v>7015391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,6 +3221,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3255,7 +3255,7 @@
         <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137861</v>
+        <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548652</v>
+        <v>548564</v>
       </c>
       <c r="R30" t="n">
-        <v>7015105</v>
+        <v>7015377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137861</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548652</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3849,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3920,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>97575</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>91837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137823</v>
+        <v>129137743</v>
       </c>
       <c r="B48" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548701</v>
+        <v>548589</v>
       </c>
       <c r="R48" t="n">
-        <v>7015210</v>
+        <v>7015420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5319,7 +5324,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5359,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5399,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5426,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137856</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548522</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5501,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>96823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548701</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,11 +5599,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B52" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R52" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,10 +5722,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R53" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>97576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548553</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137760</v>
+        <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>97575</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548553</v>
+        <v>548565</v>
       </c>
       <c r="R4" t="n">
-        <v>7015318</v>
+        <v>7015377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137865</v>
+        <v>129137880</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548447</v>
+        <v>548645</v>
       </c>
       <c r="R5" t="n">
-        <v>7015454</v>
+        <v>7015108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137880</v>
+        <v>129137777</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548645</v>
+        <v>548714</v>
       </c>
       <c r="R6" t="n">
-        <v>7015108</v>
+        <v>7015050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B7" t="n">
-        <v>57831</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R7" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137733</v>
+        <v>129137808</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548570</v>
+        <v>548646</v>
       </c>
       <c r="R9" t="n">
-        <v>7015444</v>
+        <v>7015414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137808</v>
+        <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548646</v>
+        <v>548591</v>
       </c>
       <c r="R10" t="n">
-        <v>7015414</v>
+        <v>7015389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137765</v>
+        <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>97581</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548554</v>
+        <v>548676</v>
       </c>
       <c r="R17" t="n">
-        <v>7015316</v>
+        <v>7015168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137734</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>97582</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548676</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015168</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,7 +3255,7 @@
         <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3454,7 +3459,7 @@
         <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137861</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548652</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015105</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>97576</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97575</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4143,7 +4143,7 @@
         <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R38" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,32 +4334,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R39" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R46" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R48" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5324,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5426,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5531,7 +5531,7 @@
         <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B52" t="n">
         <v>91540</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R52" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B53" t="n">
         <v>91540</v>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R53" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R6" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>57831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R7" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137808</v>
+        <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548646</v>
+        <v>548591</v>
       </c>
       <c r="R9" t="n">
-        <v>7015414</v>
+        <v>7015389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R10" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,7 +3255,7 @@
         <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3467,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,10 +3548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3559,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,32 +3844,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>97576</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>91838</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R44" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137864</v>
+        <v>129137755</v>
       </c>
       <c r="B45" t="n">
-        <v>80147</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548644</v>
+        <v>548568</v>
       </c>
       <c r="R45" t="n">
-        <v>7015111</v>
+        <v>7015450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137856</v>
+        <v>129137743</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548522</v>
+        <v>548589</v>
       </c>
       <c r="R48" t="n">
-        <v>7015382</v>
+        <v>7015420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5324,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5426,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137856</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548522</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5531,7 +5531,7 @@
         <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137760</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>97577</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548553</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015318</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R4" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137880</v>
+        <v>129137777</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548645</v>
+        <v>548714</v>
       </c>
       <c r="R5" t="n">
-        <v>7015108</v>
+        <v>7015050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1066,7 @@
         <v>129137865</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137777</v>
+        <v>129137880</v>
       </c>
       <c r="B7" t="n">
-        <v>57831</v>
+        <v>80148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548714</v>
+        <v>548645</v>
       </c>
       <c r="R7" t="n">
-        <v>7015050</v>
+        <v>7015108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R9" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137808</v>
+        <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548646</v>
+        <v>548591</v>
       </c>
       <c r="R10" t="n">
-        <v>7015414</v>
+        <v>7015389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129137904</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129137879</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>129137799</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B19" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R27" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R28" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137861</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>80177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548652</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015105</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3559,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137756</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548564</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97577</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>97581</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
         <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B40" t="n">
-        <v>91993</v>
+        <v>80176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R40" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B41" t="n">
-        <v>80174</v>
+        <v>91996</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R41" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4633,7 +4633,7 @@
         <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>129137755</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137743</v>
+        <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>96829</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548589</v>
+        <v>548701</v>
       </c>
       <c r="R48" t="n">
-        <v>7015420</v>
+        <v>7015210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5528,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
-        <v>96825</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91543</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>80185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548553</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137760</v>
+        <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548553</v>
+        <v>548565</v>
       </c>
       <c r="R4" t="n">
-        <v>7015318</v>
+        <v>7015377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>57831</v>
+        <v>91843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R5" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137865</v>
+        <v>129137777</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548447</v>
+        <v>548714</v>
       </c>
       <c r="R6" t="n">
-        <v>7015454</v>
+        <v>7015050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129137880</v>
       </c>
       <c r="B7" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137733</v>
+        <v>129137881</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548570</v>
+        <v>548591</v>
       </c>
       <c r="R8" t="n">
-        <v>7015444</v>
+        <v>7015389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137808</v>
+        <v>129137894</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548646</v>
+        <v>548514</v>
       </c>
       <c r="R9" t="n">
-        <v>7015414</v>
+        <v>7015402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R10" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137894</v>
+        <v>129137808</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548514</v>
+        <v>548646</v>
       </c>
       <c r="R11" t="n">
-        <v>7015402</v>
+        <v>7015414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>129137904</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129137879</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
         <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3056,7 +3056,7 @@
         <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>129137785</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137756</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548564</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137861</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>80177</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548652</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015105</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137861</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>80178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548652</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137756</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548564</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015377</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3750,7 +3750,7 @@
         <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R38" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,32 +4334,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R39" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>80176</v>
+        <v>91998</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R40" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>91996</v>
+        <v>80177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R41" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4633,7 +4633,7 @@
         <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137864</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>91843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548644</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015111</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137755</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>91841</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548568</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015450</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,7 +5026,7 @@
         <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137865</v>
+        <v>129137880</v>
       </c>
       <c r="B5" t="n">
-        <v>91843</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548447</v>
+        <v>548645</v>
       </c>
       <c r="R5" t="n">
-        <v>7015454</v>
+        <v>7015108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137777</v>
+        <v>129137865</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>91847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548714</v>
+        <v>548447</v>
       </c>
       <c r="R6" t="n">
-        <v>7015050</v>
+        <v>7015454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129137880</v>
+        <v>129137777</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548645</v>
+        <v>548714</v>
       </c>
       <c r="R7" t="n">
-        <v>7015108</v>
+        <v>7015050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R8" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137894</v>
+        <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548514</v>
+        <v>548591</v>
       </c>
       <c r="R9" t="n">
-        <v>7015402</v>
+        <v>7015389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,7 +1464,7 @@
         <v>129137733</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137808</v>
+        <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548646</v>
+        <v>548514</v>
       </c>
       <c r="R11" t="n">
-        <v>7015414</v>
+        <v>7015402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
         <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,7 +2857,7 @@
         <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137841</v>
+        <v>129137785</v>
       </c>
       <c r="B26" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548505</v>
+        <v>548565</v>
       </c>
       <c r="R26" t="n">
-        <v>7015403</v>
+        <v>7015398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,6 +3124,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3150,32 +3155,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137785</v>
+        <v>129137841</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548565</v>
+        <v>548505</v>
       </c>
       <c r="R27" t="n">
-        <v>7015398</v>
+        <v>7015403</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,11 +3226,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3357,7 +3357,7 @@
         <v>129137756</v>
       </c>
       <c r="B29" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>97587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97583</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4439,7 +4439,7 @@
         <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R46" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5120,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5131,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R47" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5225,7 +5225,7 @@
         <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137856</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548522</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137743</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548589</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015420</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80185</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137760</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>97587</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548553</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015318</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>97595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R4" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129137880</v>
+        <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548645</v>
+        <v>548447</v>
       </c>
       <c r="R5" t="n">
-        <v>7015108</v>
+        <v>7015454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129137865</v>
+        <v>129137880</v>
       </c>
       <c r="B6" t="n">
-        <v>91847</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548447</v>
+        <v>548645</v>
       </c>
       <c r="R6" t="n">
-        <v>7015454</v>
+        <v>7015108</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137881</v>
+        <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548591</v>
+        <v>548570</v>
       </c>
       <c r="R9" t="n">
-        <v>7015389</v>
+        <v>7015444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137733</v>
+        <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548570</v>
+        <v>548591</v>
       </c>
       <c r="R10" t="n">
-        <v>7015444</v>
+        <v>7015389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137867</v>
+        <v>129137799</v>
       </c>
       <c r="B14" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548533</v>
+        <v>548685</v>
       </c>
       <c r="R14" t="n">
-        <v>7015374</v>
+        <v>7015011</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137867</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548533</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,7 +2158,7 @@
         <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B19" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,32 +3053,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R26" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3158,7 +3158,7 @@
         <v>129137841</v>
       </c>
       <c r="B27" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R28" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4342,7 +4342,7 @@
         <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B40" t="n">
-        <v>92002</v>
+        <v>80177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R40" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>92003</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R41" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4730,7 +4730,7 @@
         <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137755</v>
+        <v>129137741</v>
       </c>
       <c r="B44" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548568</v>
+        <v>548694</v>
       </c>
       <c r="R44" t="n">
-        <v>7015450</v>
+        <v>7015327</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,6 +4900,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4926,10 +4931,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4942,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137741</v>
+        <v>129137755</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548694</v>
+        <v>548568</v>
       </c>
       <c r="R46" t="n">
-        <v>7015327</v>
+        <v>7015450</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5099,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R47" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137823</v>
+        <v>129137743</v>
       </c>
       <c r="B48" t="n">
-        <v>96835</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548701</v>
+        <v>548589</v>
       </c>
       <c r="R48" t="n">
-        <v>7015210</v>
+        <v>7015420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5523,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137743</v>
+        <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>96843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548589</v>
+        <v>548701</v>
       </c>
       <c r="R51" t="n">
-        <v>7015420</v>
+        <v>7015210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,11 +5599,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137760</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>97595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548553</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137760</v>
+        <v>129137884</v>
       </c>
       <c r="B4" t="n">
-        <v>97595</v>
+        <v>80185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548553</v>
+        <v>548643</v>
       </c>
       <c r="R4" t="n">
-        <v>7015318</v>
+        <v>7015101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137808</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548646</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015414</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137733</v>
+        <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548570</v>
+        <v>548591</v>
       </c>
       <c r="R9" t="n">
-        <v>7015444</v>
+        <v>7015389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R10" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137799</v>
+        <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548685</v>
+        <v>548533</v>
       </c>
       <c r="R14" t="n">
-        <v>7015011</v>
+        <v>7015374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137867</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548533</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015374</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
         <v>97601</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,7 +2349,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
         <v>97601</v>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,32 +3155,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137841</v>
+        <v>129137785</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548505</v>
+        <v>548565</v>
       </c>
       <c r="R27" t="n">
-        <v>7015403</v>
+        <v>7015398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,6 +3226,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137785</v>
+        <v>129137841</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548565</v>
+        <v>548505</v>
       </c>
       <c r="R28" t="n">
-        <v>7015398</v>
+        <v>7015403</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,11 +3328,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,10 +3456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3467,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137861</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>80178</v>
+        <v>91848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548652</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015105</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>80178</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3915,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R38" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,32 +4334,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R39" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137741</v>
+        <v>129137807</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548694</v>
+        <v>548713</v>
       </c>
       <c r="R44" t="n">
-        <v>7015327</v>
+        <v>7015358</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,11 +4900,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4931,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137864</v>
+        <v>129137741</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4942,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4966,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548644</v>
+        <v>548694</v>
       </c>
       <c r="R45" t="n">
-        <v>7015111</v>
+        <v>7015327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5002,6 +4997,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R47" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137743</v>
+        <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>96843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548589</v>
+        <v>548701</v>
       </c>
       <c r="R48" t="n">
-        <v>7015420</v>
+        <v>7015210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5528,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137823</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
-        <v>96843</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548701</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015210</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>80185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B4" t="n">
-        <v>80185</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R4" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137734</v>
+        <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>97601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548676</v>
+        <v>548554</v>
       </c>
       <c r="R17" t="n">
-        <v>7015168</v>
+        <v>7015316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
         <v>97601</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,32 +2354,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>97601</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548676</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B42" t="n">
-        <v>80185</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R42" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,6 +4701,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4727,32 +4732,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B43" t="n">
-        <v>98724</v>
+        <v>80185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4762,10 +4767,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R43" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4798,11 +4803,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137760</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>97595</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548553</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015318</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129137736</v>
+        <v>129137760</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548565</v>
+        <v>548553</v>
       </c>
       <c r="R4" t="n">
-        <v>7015377</v>
+        <v>7015318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129137865</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137765</v>
+        <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>97601</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548554</v>
+        <v>548676</v>
       </c>
       <c r="R17" t="n">
-        <v>7015316</v>
+        <v>7015168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137734</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>97604</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548676</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015168</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,7 +2556,7 @@
         <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,32 +3155,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137785</v>
+        <v>129137841</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548565</v>
+        <v>548505</v>
       </c>
       <c r="R27" t="n">
-        <v>7015398</v>
+        <v>7015403</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,11 +3226,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3257,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137841</v>
+        <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548505</v>
+        <v>548565</v>
       </c>
       <c r="R28" t="n">
-        <v>7015403</v>
+        <v>7015398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3328,6 +3323,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137842</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548531</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015376</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3467,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,32 +3548,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137861</v>
       </c>
       <c r="B31" t="n">
-        <v>91848</v>
+        <v>80178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548652</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3750,7 +3750,7 @@
         <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
         <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>129137752</v>
       </c>
       <c r="B41" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>80185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R42" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,11 +4701,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4732,32 +4727,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R43" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4803,6 +4798,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4997,11 +4997,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5028,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137755</v>
+        <v>129137741</v>
       </c>
       <c r="B46" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548568</v>
+        <v>548694</v>
       </c>
       <c r="R46" t="n">
-        <v>7015450</v>
+        <v>7015327</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5099,6 +5094,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R47" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5225,7 +5225,7 @@
         <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>96843</v>
+        <v>96846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5628,7 +5628,7 @@
         <v>129137735</v>
       </c>
       <c r="B52" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>129137737</v>
       </c>
       <c r="B53" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>129137839</v>
       </c>
       <c r="B54" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80185</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137733</v>
+        <v>129137894</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548570</v>
+        <v>548514</v>
       </c>
       <c r="R8" t="n">
-        <v>7015444</v>
+        <v>7015402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R9" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137808</v>
+        <v>129137733</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548646</v>
+        <v>548570</v>
       </c>
       <c r="R10" t="n">
-        <v>7015414</v>
+        <v>7015444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137894</v>
+        <v>129137881</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548514</v>
+        <v>548591</v>
       </c>
       <c r="R11" t="n">
-        <v>7015402</v>
+        <v>7015389</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137734</v>
+        <v>129137765</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>97604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548676</v>
+        <v>548554</v>
       </c>
       <c r="R17" t="n">
-        <v>7015168</v>
+        <v>7015316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137765</v>
+        <v>129137767</v>
       </c>
       <c r="B18" t="n">
         <v>97604</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548554</v>
+        <v>548518</v>
       </c>
       <c r="R18" t="n">
-        <v>7015316</v>
+        <v>7015319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,32 +2354,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137767</v>
+        <v>129137734</v>
       </c>
       <c r="B19" t="n">
-        <v>97604</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548518</v>
+        <v>548676</v>
       </c>
       <c r="R19" t="n">
-        <v>7015319</v>
+        <v>7015168</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R20" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R21" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,32 +3053,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R26" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137785</v>
+        <v>129137742</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548565</v>
+        <v>548676</v>
       </c>
       <c r="R28" t="n">
-        <v>7015398</v>
+        <v>7015391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>35 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R29" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137756</v>
+        <v>129137784</v>
       </c>
       <c r="B30" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548564</v>
+        <v>548583</v>
       </c>
       <c r="R30" t="n">
-        <v>7015377</v>
+        <v>7015438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,6 +3522,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3548,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137861</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>80178</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548652</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015105</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B33" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R33" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3981,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R35" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,11 +4017,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>80177</v>
+        <v>92006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R40" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>92006</v>
+        <v>80177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R41" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R46" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5094,11 +5094,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5125,10 +5120,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5131,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R47" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137823</v>
+        <v>129137854</v>
       </c>
       <c r="B48" t="n">
-        <v>96846</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548701</v>
+        <v>548577</v>
       </c>
       <c r="R48" t="n">
-        <v>7015210</v>
+        <v>7015456</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5523,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137854</v>
+        <v>129137823</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>96846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548577</v>
+        <v>548701</v>
       </c>
       <c r="R51" t="n">
-        <v>7015456</v>
+        <v>7015210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,11 +5599,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>80185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137894</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548514</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015402</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137733</v>
+        <v>129137881</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548570</v>
+        <v>548591</v>
       </c>
       <c r="R10" t="n">
-        <v>7015444</v>
+        <v>7015389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129137881</v>
+        <v>129137894</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548591</v>
+        <v>548514</v>
       </c>
       <c r="R11" t="n">
-        <v>7015389</v>
+        <v>7015402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137867</v>
+        <v>129137798</v>
       </c>
       <c r="B14" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548533</v>
+        <v>548681</v>
       </c>
       <c r="R14" t="n">
-        <v>7015374</v>
+        <v>7015144</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137798</v>
+        <v>129137867</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548681</v>
+        <v>548533</v>
       </c>
       <c r="R16" t="n">
-        <v>7015144</v>
+        <v>7015374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2129,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129137765</v>
+        <v>129137734</v>
       </c>
       <c r="B17" t="n">
-        <v>97604</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548554</v>
+        <v>548676</v>
       </c>
       <c r="R17" t="n">
-        <v>7015316</v>
+        <v>7015168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129137767</v>
+        <v>129137765</v>
       </c>
       <c r="B18" t="n">
         <v>97604</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548518</v>
+        <v>548554</v>
       </c>
       <c r="R18" t="n">
-        <v>7015319</v>
+        <v>7015316</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129137734</v>
+        <v>129137767</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>97604</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548676</v>
+        <v>548518</v>
       </c>
       <c r="R19" t="n">
-        <v>7015168</v>
+        <v>7015319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>11 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R20" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R21" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137756</v>
+        <v>129137861</v>
       </c>
       <c r="B29" t="n">
-        <v>91851</v>
+        <v>80178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548564</v>
+        <v>548652</v>
       </c>
       <c r="R29" t="n">
-        <v>7015377</v>
+        <v>7015105</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,32 +3451,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137784</v>
+        <v>129137842</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548583</v>
+        <v>548531</v>
       </c>
       <c r="R30" t="n">
-        <v>7015438</v>
+        <v>7015376</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,11 +3522,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3553,10 +3548,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,21 +3559,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R31" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R33" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3860,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R34" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3920,6 +3915,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B40" t="n">
-        <v>92006</v>
+        <v>80177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R40" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R41" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137755</v>
+        <v>129137807</v>
       </c>
       <c r="B44" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548568</v>
+        <v>548713</v>
       </c>
       <c r="R44" t="n">
-        <v>7015450</v>
+        <v>7015358</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129137854</v>
+        <v>129137823</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>96846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548577</v>
+        <v>548701</v>
       </c>
       <c r="R48" t="n">
-        <v>7015456</v>
+        <v>7015210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5324,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R49" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5426,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R50" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5501,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5528,32 +5523,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137823</v>
+        <v>129137743</v>
       </c>
       <c r="B51" t="n">
-        <v>96846</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548701</v>
+        <v>548589</v>
       </c>
       <c r="R51" t="n">
-        <v>7015210</v>
+        <v>7015420</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5599,6 +5594,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5625,7 +5625,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B52" t="n">
         <v>91553</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R52" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B53" t="n">
         <v>91553</v>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R53" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80185</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137733</v>
+        <v>129137808</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548570</v>
+        <v>548646</v>
       </c>
       <c r="R8" t="n">
-        <v>7015444</v>
+        <v>7015414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137808</v>
+        <v>129137733</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548646</v>
+        <v>548570</v>
       </c>
       <c r="R9" t="n">
-        <v>7015414</v>
+        <v>7015444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1854,7 +1854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R14" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137799</v>
+        <v>129137798</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548685</v>
+        <v>548681</v>
       </c>
       <c r="R15" t="n">
-        <v>7015011</v>
+        <v>7015144</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R20" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R21" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R22" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R23" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B24" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R24" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2925,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R25" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3022,11 +3027,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3053,32 +3053,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129137785</v>
+        <v>129137841</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548565</v>
+        <v>548505</v>
       </c>
       <c r="R26" t="n">
-        <v>7015398</v>
+        <v>7015403</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,11 +3124,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3155,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129137841</v>
+        <v>129137742</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3166,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3190,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548505</v>
+        <v>548676</v>
       </c>
       <c r="R27" t="n">
-        <v>7015403</v>
+        <v>7015391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,6 +3221,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,32 +3252,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129137742</v>
+        <v>129137785</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548676</v>
+        <v>548565</v>
       </c>
       <c r="R28" t="n">
-        <v>7015391</v>
+        <v>7015398</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>35 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B29" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R29" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,10 +3456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129137842</v>
+        <v>129137756</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3467,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548531</v>
+        <v>548564</v>
       </c>
       <c r="R30" t="n">
-        <v>7015376</v>
+        <v>7015377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3548,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129137756</v>
+        <v>129137842</v>
       </c>
       <c r="B31" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3559,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548564</v>
+        <v>548531</v>
       </c>
       <c r="R31" t="n">
-        <v>7015377</v>
+        <v>7015376</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R32" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,11 +3721,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R36" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B37" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R37" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B40" t="n">
-        <v>80177</v>
+        <v>92006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R40" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B41" t="n">
-        <v>92006</v>
+        <v>80177</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R41" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B42" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R42" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,6 +4701,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4727,32 +4732,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4762,10 +4767,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R43" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4798,11 +4803,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137807</v>
+        <v>129137741</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548713</v>
+        <v>548694</v>
       </c>
       <c r="R44" t="n">
-        <v>7015358</v>
+        <v>7015327</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,6 +4900,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,10 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137864</v>
+        <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5039,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548644</v>
+        <v>548713</v>
       </c>
       <c r="R46" t="n">
-        <v>7015111</v>
+        <v>7015358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5120,10 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5131,21 +5136,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R47" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5191,11 +5196,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5319,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5625,7 +5625,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129137737</v>
+        <v>129137735</v>
       </c>
       <c r="B52" t="n">
         <v>91553</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548584</v>
+        <v>548711</v>
       </c>
       <c r="R52" t="n">
-        <v>7015355</v>
+        <v>7015346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129137735</v>
+        <v>129137737</v>
       </c>
       <c r="B53" t="n">
         <v>91553</v>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548711</v>
+        <v>548584</v>
       </c>
       <c r="R53" t="n">
-        <v>7015346</v>
+        <v>7015355</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>80185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R2" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R3" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129137808</v>
+        <v>129137733</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548646</v>
+        <v>548570</v>
       </c>
       <c r="R8" t="n">
-        <v>7015414</v>
+        <v>7015444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137733</v>
+        <v>129137808</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548570</v>
+        <v>548646</v>
       </c>
       <c r="R9" t="n">
-        <v>7015444</v>
+        <v>7015414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129137799</v>
+        <v>129137867</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548685</v>
+        <v>548533</v>
       </c>
       <c r="R14" t="n">
-        <v>7015011</v>
+        <v>7015374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129137798</v>
+        <v>129137799</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548681</v>
+        <v>548685</v>
       </c>
       <c r="R15" t="n">
-        <v>7015144</v>
+        <v>7015011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129137867</v>
+        <v>129137798</v>
       </c>
       <c r="B16" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548533</v>
+        <v>548681</v>
       </c>
       <c r="R16" t="n">
-        <v>7015374</v>
+        <v>7015144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2129,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129137855</v>
+        <v>129137754</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548490</v>
+        <v>548715</v>
       </c>
       <c r="R24" t="n">
-        <v>7015418</v>
+        <v>7015352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2925,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129137754</v>
+        <v>129137855</v>
       </c>
       <c r="B25" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548715</v>
+        <v>548490</v>
       </c>
       <c r="R25" t="n">
-        <v>7015352</v>
+        <v>7015418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,6 +3022,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129137784</v>
+        <v>129137861</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548583</v>
+        <v>548652</v>
       </c>
       <c r="R29" t="n">
-        <v>7015438</v>
+        <v>7015105</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3425,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3650,32 +3645,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129137861</v>
+        <v>129137784</v>
       </c>
       <c r="B32" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3685,10 +3680,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548652</v>
+        <v>548583</v>
       </c>
       <c r="R32" t="n">
-        <v>7015105</v>
+        <v>7015438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3721,6 +3716,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>26 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137809</v>
+        <v>129137850</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548622</v>
+        <v>548629</v>
       </c>
       <c r="R33" t="n">
-        <v>7015434</v>
+        <v>7015262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,6 +3818,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3844,10 +3849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129137850</v>
+        <v>129137809</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3860,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548629</v>
+        <v>548622</v>
       </c>
       <c r="R34" t="n">
-        <v>7015262</v>
+        <v>7015434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,11 +3920,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R38" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,11 +4308,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4339,32 +4334,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4374,10 +4369,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R39" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4410,6 +4405,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4630,32 +4630,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129137897</v>
+        <v>129137885</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548644</v>
+        <v>548594</v>
       </c>
       <c r="R42" t="n">
-        <v>7015104</v>
+        <v>7015380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,11 +4701,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4732,32 +4727,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129137885</v>
+        <v>129137897</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548594</v>
+        <v>548644</v>
       </c>
       <c r="R43" t="n">
-        <v>7015380</v>
+        <v>7015104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4803,6 +4798,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137741</v>
+        <v>129137864</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548694</v>
+        <v>548644</v>
       </c>
       <c r="R44" t="n">
-        <v>7015327</v>
+        <v>7015111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4900,11 +4900,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4931,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137755</v>
+        <v>129137807</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4942,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4966,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548568</v>
+        <v>548713</v>
       </c>
       <c r="R45" t="n">
-        <v>7015450</v>
+        <v>7015358</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137807</v>
+        <v>129137755</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5039,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548713</v>
+        <v>548568</v>
       </c>
       <c r="R46" t="n">
-        <v>7015358</v>
+        <v>7015450</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5125,10 +5120,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129137864</v>
+        <v>129137741</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5136,21 +5131,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548644</v>
+        <v>548694</v>
       </c>
       <c r="R47" t="n">
-        <v>7015111</v>
+        <v>7015327</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5319,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137743</v>
+        <v>129137856</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548589</v>
+        <v>548522</v>
       </c>
       <c r="R49" t="n">
-        <v>7015420</v>
+        <v>7015382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137854</v>
+        <v>129137743</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548577</v>
+        <v>548589</v>
       </c>
       <c r="R50" t="n">
-        <v>7015456</v>
+        <v>7015420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137856</v>
+        <v>129137854</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548522</v>
+        <v>548577</v>
       </c>
       <c r="R51" t="n">
-        <v>7015382</v>
+        <v>7015456</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 42776-2025 artfynd.xlsx
+++ b/artfynd/A 42776-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129137884</v>
+        <v>129137736</v>
       </c>
       <c r="B2" t="n">
-        <v>80185</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548643</v>
+        <v>548565</v>
       </c>
       <c r="R2" t="n">
-        <v>7015101</v>
+        <v>7015377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129137736</v>
+        <v>129137884</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548565</v>
+        <v>548643</v>
       </c>
       <c r="R3" t="n">
-        <v>7015377</v>
+        <v>7015101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129137808</v>
+        <v>129137881</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548646</v>
+        <v>548591</v>
       </c>
       <c r="R9" t="n">
-        <v>7015414</v>
+        <v>7015389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129137881</v>
+        <v>129137808</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548591</v>
+        <v>548646</v>
       </c>
       <c r="R10" t="n">
-        <v>7015389</v>
+        <v>7015414</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2451,32 +2451,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129137892</v>
+        <v>129137851</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548608</v>
+        <v>548656</v>
       </c>
       <c r="R20" t="n">
-        <v>7015378</v>
+        <v>7015292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129137851</v>
+        <v>129137892</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548656</v>
+        <v>548608</v>
       </c>
       <c r="R21" t="n">
-        <v>7015292</v>
+        <v>7015378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,32 +2655,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129137891</v>
+        <v>129137843</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548627</v>
+        <v>548488</v>
       </c>
       <c r="R22" t="n">
-        <v>7015253</v>
+        <v>7015296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2726,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129137843</v>
+        <v>129137891</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548488</v>
+        <v>548627</v>
       </c>
       <c r="R23" t="n">
-        <v>7015296</v>
+        <v>7015253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3747,32 +3747,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129137850</v>
+        <v>129137868</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548629</v>
+        <v>548650</v>
       </c>
       <c r="R33" t="n">
-        <v>7015262</v>
+        <v>7015104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,32 +3941,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129137868</v>
+        <v>129137850</v>
       </c>
       <c r="B35" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3981,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548650</v>
+        <v>548629</v>
       </c>
       <c r="R35" t="n">
-        <v>7015104</v>
+        <v>7015262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4017,6 +4012,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4043,10 +4043,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129137866</v>
+        <v>129137907</v>
       </c>
       <c r="B36" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4054,21 +4054,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548507</v>
+        <v>548435</v>
       </c>
       <c r="R36" t="n">
-        <v>7015403</v>
+        <v>7015446</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129137907</v>
+        <v>129137866</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548435</v>
+        <v>548507</v>
       </c>
       <c r="R37" t="n">
-        <v>7015446</v>
+        <v>7015403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,32 +4237,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129137838</v>
+        <v>129137853</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548507</v>
+        <v>548592</v>
       </c>
       <c r="R38" t="n">
-        <v>7015403</v>
+        <v>7015417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4308,6 +4308,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4334,32 +4339,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129137853</v>
+        <v>129137838</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4369,10 +4374,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548592</v>
+        <v>548507</v>
       </c>
       <c r="R39" t="n">
-        <v>7015417</v>
+        <v>7015403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4405,11 +4410,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4436,32 +4436,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129137752</v>
+        <v>129137770</v>
       </c>
       <c r="B40" t="n">
-        <v>92006</v>
+        <v>80177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548711</v>
+        <v>548566</v>
       </c>
       <c r="R40" t="n">
-        <v>7015343</v>
+        <v>7015327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,32 +4533,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129137770</v>
+        <v>129137752</v>
       </c>
       <c r="B41" t="n">
-        <v>80177</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548566</v>
+        <v>548711</v>
       </c>
       <c r="R41" t="n">
-        <v>7015327</v>
+        <v>7015343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129137864</v>
+        <v>129137755</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548644</v>
+        <v>548568</v>
       </c>
       <c r="R44" t="n">
-        <v>7015111</v>
+        <v>7015450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129137807</v>
+        <v>129137864</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548713</v>
+        <v>548644</v>
       </c>
       <c r="R45" t="n">
-        <v>7015358</v>
+        <v>7015111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129137755</v>
+        <v>129137807</v>
       </c>
       <c r="B46" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548568</v>
+        <v>548713</v>
       </c>
       <c r="R46" t="n">
-        <v>7015450</v>
+        <v>7015358</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129137856</v>
+        <v>129137743</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548522</v>
+        <v>548589</v>
       </c>
       <c r="R49" t="n">
-        <v>7015382</v>
+        <v>7015420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129137743</v>
+        <v>129137854</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548589</v>
+        <v>548577</v>
       </c>
       <c r="R50" t="n">
-        <v>7015420</v>
+        <v>7015456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129137854</v>
+        <v>129137856</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548577</v>
+        <v>548522</v>
       </c>
       <c r="R51" t="n">
-        <v>7015456</v>
+        <v>7015382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
